--- a/Bases_de_Dados/FootyStats/Czech Republic First League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Czech Republic First League_20252026.xlsx
@@ -41913,7 +41913,7 @@
         <v>10</v>
       </c>
       <c r="AV190" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW190" t="n">
         <v>9</v>
@@ -41925,7 +41925,7 @@
         <v>19</v>
       </c>
       <c r="AZ190" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA190" t="n">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Czech Republic First League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Czech Republic First League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP190"/>
+  <dimension ref="A1:BP193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ4" t="n">
         <v>0.33</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ12" t="n">
         <v>0.33</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -4184,7 +4184,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR17" t="n">
         <v>1.66</v>
@@ -4399,7 +4399,7 @@
         <v>3</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.25</v>
@@ -4835,7 +4835,7 @@
         <v>1</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ20" t="n">
         <v>1.33</v>
@@ -5925,7 +5925,7 @@
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ25" t="n">
         <v>0.82</v>
@@ -6146,7 +6146,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR26" t="n">
         <v>1.44</v>
@@ -7451,7 +7451,7 @@
         <v>3</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ32" t="n">
         <v>1.25</v>
@@ -7890,7 +7890,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR34" t="n">
         <v>0.96</v>
@@ -8541,10 +8541,10 @@
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR37" t="n">
         <v>1.42</v>
@@ -8980,7 +8980,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR39" t="n">
         <v>1.88</v>
@@ -9413,7 +9413,7 @@
         <v>0.5</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ41" t="n">
         <v>1.33</v>
@@ -10288,7 +10288,7 @@
         <v>1</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR45" t="n">
         <v>1.7</v>
@@ -10724,7 +10724,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR47" t="n">
         <v>0.65</v>
@@ -11157,7 +11157,7 @@
         <v>0</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ49" t="n">
         <v>1</v>
@@ -11814,7 +11814,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR52" t="n">
         <v>1.26</v>
@@ -12029,7 +12029,7 @@
         <v>0.5</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ53" t="n">
         <v>0.62</v>
@@ -12465,7 +12465,7 @@
         <v>0.25</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ55" t="n">
         <v>0.33</v>
@@ -13776,7 +13776,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR61" t="n">
         <v>1.14</v>
@@ -14427,7 +14427,7 @@
         <v>0.25</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ64" t="n">
         <v>1</v>
@@ -14645,7 +14645,7 @@
         <v>0.5</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ65" t="n">
         <v>1.15</v>
@@ -14866,7 +14866,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ66" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR66" t="n">
         <v>0.92</v>
@@ -15081,7 +15081,7 @@
         <v>2.5</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ67" t="n">
         <v>1.83</v>
@@ -15302,7 +15302,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR68" t="n">
         <v>1.99</v>
@@ -15520,7 +15520,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR69" t="n">
         <v>1.4</v>
@@ -18136,7 +18136,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ81" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR81" t="n">
         <v>1.65</v>
@@ -18790,7 +18790,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ84" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR84" t="n">
         <v>1.35</v>
@@ -19005,7 +19005,7 @@
         <v>1</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ85" t="n">
         <v>0.62</v>
@@ -19441,7 +19441,7 @@
         <v>2.6</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ87" t="n">
         <v>1.83</v>
@@ -19880,7 +19880,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ89" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR89" t="n">
         <v>1.22</v>
@@ -20095,7 +20095,7 @@
         <v>0.8</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ90" t="n">
         <v>1</v>
@@ -22057,7 +22057,7 @@
         <v>0.4</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ99" t="n">
         <v>1.09</v>
@@ -22278,7 +22278,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ100" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR100" t="n">
         <v>1.27</v>
@@ -22929,7 +22929,7 @@
         <v>2</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ103" t="n">
         <v>2.17</v>
@@ -23368,7 +23368,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR105" t="n">
         <v>2.02</v>
@@ -24673,7 +24673,7 @@
         <v>1.83</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ111" t="n">
         <v>2</v>
@@ -25112,7 +25112,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR113" t="n">
         <v>1.32</v>
@@ -25330,7 +25330,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ114" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR114" t="n">
         <v>1.08</v>
@@ -25763,10 +25763,10 @@
         <v>1.33</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR116" t="n">
         <v>1.53</v>
@@ -26635,7 +26635,7 @@
         <v>0.5</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ120" t="n">
         <v>1.09</v>
@@ -27946,7 +27946,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR126" t="n">
         <v>2.44</v>
@@ -28161,7 +28161,7 @@
         <v>1.5</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ127" t="n">
         <v>1.15</v>
@@ -28382,7 +28382,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR128" t="n">
         <v>1.51</v>
@@ -29033,7 +29033,7 @@
         <v>1.5</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ131" t="n">
         <v>1.5</v>
@@ -29472,7 +29472,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ133" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR133" t="n">
         <v>2.39</v>
@@ -30780,7 +30780,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR139" t="n">
         <v>1.54</v>
@@ -31431,7 +31431,7 @@
         <v>1.75</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ142" t="n">
         <v>2</v>
@@ -31652,7 +31652,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ143" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR143" t="n">
         <v>1.47</v>
@@ -31867,7 +31867,7 @@
         <v>0.67</v>
       </c>
       <c r="AP144" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ144" t="n">
         <v>0.62</v>
@@ -32524,7 +32524,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ147" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR147" t="n">
         <v>1.24</v>
@@ -33393,7 +33393,7 @@
         <v>1</v>
       </c>
       <c r="AP151" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ151" t="n">
         <v>1</v>
@@ -34268,7 +34268,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ155" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR155" t="n">
         <v>1.67</v>
@@ -34483,7 +34483,7 @@
         <v>1.2</v>
       </c>
       <c r="AP156" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ156" t="n">
         <v>1.15</v>
@@ -35355,10 +35355,10 @@
         <v>1.56</v>
       </c>
       <c r="AP160" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ160" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR160" t="n">
         <v>1.69</v>
@@ -36012,7 +36012,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ163" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR163" t="n">
         <v>1.46</v>
@@ -37099,7 +37099,7 @@
         <v>2</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ168" t="n">
         <v>2</v>
@@ -37535,7 +37535,7 @@
         <v>2</v>
       </c>
       <c r="AP170" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ170" t="n">
         <v>2.17</v>
@@ -37756,7 +37756,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ171" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR171" t="n">
         <v>1.54</v>
@@ -38189,10 +38189,10 @@
         <v>1.7</v>
       </c>
       <c r="AP173" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ173" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR173" t="n">
         <v>1.49</v>
@@ -41974,6 +41974,660 @@
       </c>
       <c r="BP190" t="n">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" t="n">
+        <v>8283056</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Czech Republic First League</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="n">
+        <v>46082.375</v>
+      </c>
+      <c r="F191" t="n">
+        <v>24</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Karviná</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Slovácko</t>
+        </is>
+      </c>
+      <c r="I191" t="n">
+        <v>0</v>
+      </c>
+      <c r="J191" t="n">
+        <v>1</v>
+      </c>
+      <c r="K191" t="n">
+        <v>1</v>
+      </c>
+      <c r="L191" t="n">
+        <v>0</v>
+      </c>
+      <c r="M191" t="n">
+        <v>2</v>
+      </c>
+      <c r="N191" t="n">
+        <v>2</v>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>['39', '90+7']</t>
+        </is>
+      </c>
+      <c r="Q191" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R191" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S191" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T191" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U191" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V191" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="W191" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X191" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y191" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z191" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AA191" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB191" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AC191" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD191" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE191" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF191" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG191" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH191" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AI191" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ191" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AK191" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL191" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM191" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AN191" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AO191" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AP191" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ191" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AR191" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS191" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AT191" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AU191" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV191" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW191" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX191" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY191" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ191" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA191" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB191" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC191" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD191" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BE191" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF191" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BG191" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH191" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="BI191" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BJ191" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BK191" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BL191" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BM191" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BN191" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BO191" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BP191" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" t="n">
+        <v>8283071</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Czech Republic First League</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="n">
+        <v>46082.47916666666</v>
+      </c>
+      <c r="F192" t="n">
+        <v>24</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Zlín</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Viktoria Plzeň</t>
+        </is>
+      </c>
+      <c r="I192" t="n">
+        <v>1</v>
+      </c>
+      <c r="J192" t="n">
+        <v>0</v>
+      </c>
+      <c r="K192" t="n">
+        <v>1</v>
+      </c>
+      <c r="L192" t="n">
+        <v>3</v>
+      </c>
+      <c r="M192" t="n">
+        <v>0</v>
+      </c>
+      <c r="N192" t="n">
+        <v>3</v>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>['3', '71', '80']</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q192" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="R192" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S192" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="T192" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U192" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="V192" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="W192" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X192" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Y192" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z192" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA192" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB192" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC192" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD192" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE192" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF192" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AG192" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH192" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AI192" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ192" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AK192" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL192" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM192" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AN192" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AO192" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AP192" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ192" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR192" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS192" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AT192" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AU192" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV192" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW192" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX192" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY192" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ192" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA192" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB192" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC192" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD192" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BE192" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF192" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BG192" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH192" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI192" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BJ192" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BK192" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BL192" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BM192" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BN192" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BO192" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BP192" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" t="n">
+        <v>8283169</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Czech Republic First League</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="n">
+        <v>46082.60416666666</v>
+      </c>
+      <c r="F193" t="n">
+        <v>24</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Sigma Olomouc</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Bohemians 1905</t>
+        </is>
+      </c>
+      <c r="I193" t="n">
+        <v>1</v>
+      </c>
+      <c r="J193" t="n">
+        <v>0</v>
+      </c>
+      <c r="K193" t="n">
+        <v>1</v>
+      </c>
+      <c r="L193" t="n">
+        <v>1</v>
+      </c>
+      <c r="M193" t="n">
+        <v>0</v>
+      </c>
+      <c r="N193" t="n">
+        <v>1</v>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>['26']</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q193" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R193" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S193" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T193" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U193" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V193" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="W193" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X193" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y193" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z193" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA193" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AB193" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="AC193" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD193" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AE193" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF193" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG193" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH193" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AI193" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ193" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK193" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM193" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN193" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO193" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AP193" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ193" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR193" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AS193" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AT193" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AU193" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV193" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW193" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX193" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY193" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ193" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA193" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB193" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC193" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD193" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BE193" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF193" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BG193" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH193" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="BI193" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ193" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BK193" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BL193" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BM193" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BN193" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BO193" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BP193" t="n">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Czech Republic First League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Czech Republic First League_20252026.xlsx
@@ -41256,16 +41256,16 @@
         <v>2.83</v>
       </c>
       <c r="AU187" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV187" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW187" t="n">
         <v>5</v>
       </c>
-      <c r="AV187" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW187" t="n">
-        <v>4</v>
-      </c>
       <c r="AX187" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY187" t="n">
         <v>9</v>

--- a/Bases_de_Dados/FootyStats/Czech Republic First League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Czech Republic First League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP193"/>
+  <dimension ref="A1:BP196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.25</v>
@@ -1350,7 +1350,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ5" t="n">
         <v>0.62</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ7" t="n">
         <v>1</v>
@@ -2222,7 +2222,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -3094,7 +3094,7 @@
         <v>2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ14" t="n">
         <v>2.17</v>
@@ -3966,7 +3966,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ17" t="n">
         <v>1.25</v>
@@ -4838,7 +4838,7 @@
         <v>2</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR20" t="n">
         <v>1.21</v>
@@ -5053,7 +5053,7 @@
         <v>3</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ21" t="n">
         <v>2.17</v>
@@ -5710,7 +5710,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AR24" t="n">
         <v>1.82</v>
@@ -5928,7 +5928,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR25" t="n">
         <v>1.29</v>
@@ -6797,7 +6797,7 @@
         <v>1</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ29" t="n">
         <v>1.83</v>
@@ -8105,7 +8105,7 @@
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ35" t="n">
         <v>1</v>
@@ -9416,7 +9416,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR41" t="n">
         <v>1.39</v>
@@ -9631,7 +9631,7 @@
         <v>2</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ42" t="n">
         <v>1.83</v>
@@ -10506,7 +10506,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AR46" t="n">
         <v>1.86</v>
@@ -11375,7 +11375,7 @@
         <v>2.33</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ50" t="n">
         <v>1.83</v>
@@ -12468,7 +12468,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AR55" t="n">
         <v>1.39</v>
@@ -12686,7 +12686,7 @@
         <v>1</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR56" t="n">
         <v>2.07</v>
@@ -13119,10 +13119,10 @@
         <v>0</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR58" t="n">
         <v>1.35</v>
@@ -13773,7 +13773,7 @@
         <v>0.67</v>
       </c>
       <c r="AP61" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ61" t="n">
         <v>0.67</v>
@@ -16174,7 +16174,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ72" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AR72" t="n">
         <v>2.74</v>
@@ -16389,7 +16389,7 @@
         <v>1.5</v>
       </c>
       <c r="AP73" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ73" t="n">
         <v>1.5</v>
@@ -16825,7 +16825,7 @@
         <v>0.75</v>
       </c>
       <c r="AP75" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ75" t="n">
         <v>1</v>
@@ -17046,7 +17046,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR76" t="n">
         <v>0.95</v>
@@ -17261,7 +17261,7 @@
         <v>0.25</v>
       </c>
       <c r="AP77" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ77" t="n">
         <v>1.09</v>
@@ -17482,7 +17482,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ78" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR78" t="n">
         <v>1.31</v>
@@ -19877,7 +19877,7 @@
         <v>1.4</v>
       </c>
       <c r="AP89" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ89" t="n">
         <v>1.67</v>
@@ -20316,7 +20316,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ91" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR91" t="n">
         <v>1.24</v>
@@ -20531,10 +20531,10 @@
         <v>1.4</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR92" t="n">
         <v>1.34</v>
@@ -21185,7 +21185,7 @@
         <v>2</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ95" t="n">
         <v>2</v>
@@ -21406,7 +21406,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ96" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AR96" t="n">
         <v>1.35</v>
@@ -21621,10 +21621,10 @@
         <v>0.6</v>
       </c>
       <c r="AP97" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ97" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR97" t="n">
         <v>1.25</v>
@@ -23804,7 +23804,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ107" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AR107" t="n">
         <v>1.33</v>
@@ -24019,10 +24019,10 @@
         <v>1.33</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR108" t="n">
         <v>1.59</v>
@@ -24891,7 +24891,7 @@
         <v>1.29</v>
       </c>
       <c r="AP112" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ112" t="n">
         <v>1.15</v>
@@ -25109,7 +25109,7 @@
         <v>1.67</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ113" t="n">
         <v>1.67</v>
@@ -25548,7 +25548,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ115" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR115" t="n">
         <v>1.18</v>
@@ -27071,7 +27071,7 @@
         <v>0.75</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ122" t="n">
         <v>0.62</v>
@@ -27292,7 +27292,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ123" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR123" t="n">
         <v>1.38</v>
@@ -28597,7 +28597,7 @@
         <v>1.86</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ129" t="n">
         <v>1.25</v>
@@ -28818,7 +28818,7 @@
         <v>1</v>
       </c>
       <c r="AQ130" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AR130" t="n">
         <v>1.81</v>
@@ -29687,7 +29687,7 @@
         <v>0.88</v>
       </c>
       <c r="AP134" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ134" t="n">
         <v>1</v>
@@ -29908,7 +29908,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ135" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR135" t="n">
         <v>2</v>
@@ -30559,7 +30559,7 @@
         <v>2</v>
       </c>
       <c r="AP138" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ138" t="n">
         <v>2.17</v>
@@ -30777,7 +30777,7 @@
         <v>1.75</v>
       </c>
       <c r="AP139" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ139" t="n">
         <v>1.67</v>
@@ -31216,7 +31216,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ141" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR141" t="n">
         <v>1.16</v>
@@ -32306,7 +32306,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ146" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR146" t="n">
         <v>1.25</v>
@@ -32521,7 +32521,7 @@
         <v>0.44</v>
       </c>
       <c r="AP147" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ147" t="n">
         <v>0.67</v>
@@ -33175,7 +33175,7 @@
         <v>1.67</v>
       </c>
       <c r="AP150" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ150" t="n">
         <v>1.5</v>
@@ -33614,7 +33614,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ152" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AR152" t="n">
         <v>1.97</v>
@@ -33832,7 +33832,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR153" t="n">
         <v>2.06</v>
@@ -34919,7 +34919,7 @@
         <v>0.7</v>
       </c>
       <c r="AP158" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ158" t="n">
         <v>0.62</v>
@@ -35791,7 +35791,7 @@
         <v>1.8</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ162" t="n">
         <v>1.5</v>
@@ -36448,7 +36448,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ165" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR165" t="n">
         <v>2.42</v>
@@ -36666,7 +36666,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ166" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AR166" t="n">
         <v>1.36</v>
@@ -36881,7 +36881,7 @@
         <v>1</v>
       </c>
       <c r="AP167" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ167" t="n">
         <v>1.09</v>
@@ -37320,7 +37320,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR169" t="n">
         <v>2</v>
@@ -37753,7 +37753,7 @@
         <v>1.2</v>
       </c>
       <c r="AP171" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ171" t="n">
         <v>1.25</v>
@@ -39715,7 +39715,7 @@
         <v>1.2</v>
       </c>
       <c r="AP180" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ180" t="n">
         <v>1.09</v>
@@ -39936,7 +39936,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ181" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR181" t="n">
         <v>2.41</v>
@@ -40151,10 +40151,10 @@
         <v>0.36</v>
       </c>
       <c r="AP182" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ182" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AR182" t="n">
         <v>1.48</v>
@@ -40372,7 +40372,7 @@
         <v>1</v>
       </c>
       <c r="AQ183" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR183" t="n">
         <v>1.78</v>
@@ -40587,7 +40587,7 @@
         <v>0.82</v>
       </c>
       <c r="AP184" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ184" t="n">
         <v>1</v>
@@ -42628,6 +42628,660 @@
       </c>
       <c r="BP193" t="n">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" t="n">
+        <v>8283154</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Czech Republic First League</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="n">
+        <v>46088.45833333334</v>
+      </c>
+      <c r="F194" t="n">
+        <v>25</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Bohemians 1905</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Slovan Liberec</t>
+        </is>
+      </c>
+      <c r="I194" t="n">
+        <v>0</v>
+      </c>
+      <c r="J194" t="n">
+        <v>0</v>
+      </c>
+      <c r="K194" t="n">
+        <v>0</v>
+      </c>
+      <c r="L194" t="n">
+        <v>0</v>
+      </c>
+      <c r="M194" t="n">
+        <v>1</v>
+      </c>
+      <c r="N194" t="n">
+        <v>1</v>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>['-1']</t>
+        </is>
+      </c>
+      <c r="Q194" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="R194" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="S194" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="T194" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U194" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="V194" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W194" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X194" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="Y194" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z194" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AA194" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AB194" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC194" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD194" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE194" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF194" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AG194" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AH194" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI194" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ194" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AK194" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL194" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM194" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AN194" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AO194" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP194" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AQ194" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR194" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AS194" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AT194" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AU194" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV194" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW194" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX194" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY194" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ194" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA194" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB194" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC194" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD194" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BE194" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF194" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BG194" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH194" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI194" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ194" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BK194" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BL194" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BM194" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BN194" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BO194" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BP194" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" t="n">
+        <v>8283043</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Czech Republic First League</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="n">
+        <v>46088.45833333334</v>
+      </c>
+      <c r="F195" t="n">
+        <v>25</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Teplice</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Dukla Praha</t>
+        </is>
+      </c>
+      <c r="I195" t="n">
+        <v>0</v>
+      </c>
+      <c r="J195" t="n">
+        <v>0</v>
+      </c>
+      <c r="K195" t="n">
+        <v>0</v>
+      </c>
+      <c r="L195" t="n">
+        <v>0</v>
+      </c>
+      <c r="M195" t="n">
+        <v>0</v>
+      </c>
+      <c r="N195" t="n">
+        <v>0</v>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q195" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R195" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="S195" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="T195" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U195" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V195" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="W195" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X195" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y195" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z195" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA195" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AB195" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AC195" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD195" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AE195" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF195" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AG195" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH195" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI195" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ195" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AK195" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AL195" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM195" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AN195" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO195" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AP195" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AQ195" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AR195" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AS195" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AT195" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU195" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV195" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW195" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX195" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY195" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ195" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA195" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB195" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC195" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD195" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BE195" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF195" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="BG195" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH195" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI195" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BJ195" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BK195" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BL195" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BM195" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BN195" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BO195" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BP195" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" t="n">
+        <v>8283059</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Czech Republic First League</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="n">
+        <v>46088.45833333334</v>
+      </c>
+      <c r="F196" t="n">
+        <v>25</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Slovácko</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Mladá Boleslav</t>
+        </is>
+      </c>
+      <c r="I196" t="n">
+        <v>1</v>
+      </c>
+      <c r="J196" t="n">
+        <v>1</v>
+      </c>
+      <c r="K196" t="n">
+        <v>2</v>
+      </c>
+      <c r="L196" t="n">
+        <v>2</v>
+      </c>
+      <c r="M196" t="n">
+        <v>2</v>
+      </c>
+      <c r="N196" t="n">
+        <v>4</v>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>['3', '78']</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>['34', '64']</t>
+        </is>
+      </c>
+      <c r="Q196" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R196" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S196" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T196" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="U196" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V196" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="W196" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X196" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="Y196" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z196" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA196" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB196" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC196" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD196" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE196" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF196" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AG196" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH196" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AI196" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ196" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK196" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL196" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM196" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AN196" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO196" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AP196" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AQ196" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AR196" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS196" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AT196" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AU196" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV196" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW196" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX196" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY196" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ196" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA196" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB196" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC196" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD196" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BE196" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF196" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BG196" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH196" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI196" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ196" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BK196" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BL196" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM196" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN196" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BO196" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BP196" t="n">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Czech Republic First League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Czech Republic First League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP196"/>
+  <dimension ref="A1:BP197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="AQ5" t="n">
         <v>0.62</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ6" t="n">
         <v>2</v>
@@ -2004,7 +2004,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="AQ14" t="n">
         <v>2.17</v>
@@ -4617,7 +4617,7 @@
         <v>1</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ19" t="n">
         <v>1.15</v>
@@ -4838,7 +4838,7 @@
         <v>2</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="AR20" t="n">
         <v>1.21</v>
@@ -6797,7 +6797,7 @@
         <v>1</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="AQ29" t="n">
         <v>1.83</v>
@@ -7236,7 +7236,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR31" t="n">
         <v>2.03</v>
@@ -8323,7 +8323,7 @@
         <v>3</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ36" t="n">
         <v>2.17</v>
@@ -9416,7 +9416,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="AR41" t="n">
         <v>1.39</v>
@@ -10070,7 +10070,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR44" t="n">
         <v>1.13</v>
@@ -12686,7 +12686,7 @@
         <v>1</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="AR56" t="n">
         <v>2.07</v>
@@ -12904,7 +12904,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR57" t="n">
         <v>1.95</v>
@@ -13555,7 +13555,7 @@
         <v>0.33</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ60" t="n">
         <v>1.09</v>
@@ -13773,7 +13773,7 @@
         <v>0.67</v>
       </c>
       <c r="AP61" t="n">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="AQ61" t="n">
         <v>0.67</v>
@@ -16825,10 +16825,10 @@
         <v>0.75</v>
       </c>
       <c r="AP75" t="n">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR75" t="n">
         <v>1.3</v>
@@ -17046,7 +17046,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="AR76" t="n">
         <v>0.95</v>
@@ -17479,7 +17479,7 @@
         <v>1</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ78" t="n">
         <v>0.83</v>
@@ -19877,7 +19877,7 @@
         <v>1.4</v>
       </c>
       <c r="AP89" t="n">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="AQ89" t="n">
         <v>1.67</v>
@@ -20098,7 +20098,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR90" t="n">
         <v>1.44</v>
@@ -20534,7 +20534,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="AR92" t="n">
         <v>1.34</v>
@@ -21403,7 +21403,7 @@
         <v>0.33</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ96" t="n">
         <v>0.38</v>
@@ -21621,7 +21621,7 @@
         <v>0.6</v>
       </c>
       <c r="AP97" t="n">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="AQ97" t="n">
         <v>0.83</v>
@@ -23583,7 +23583,7 @@
         <v>1.67</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ106" t="n">
         <v>1.25</v>
@@ -24022,7 +24022,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="AR108" t="n">
         <v>1.59</v>
@@ -24458,7 +24458,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR110" t="n">
         <v>1.66</v>
@@ -24891,7 +24891,7 @@
         <v>1.29</v>
       </c>
       <c r="AP112" t="n">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="AQ112" t="n">
         <v>1.15</v>
@@ -27292,7 +27292,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ123" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="AR123" t="n">
         <v>1.38</v>
@@ -27728,7 +27728,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ125" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR125" t="n">
         <v>1.11</v>
@@ -28379,7 +28379,7 @@
         <v>1.86</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ128" t="n">
         <v>1.67</v>
@@ -29687,7 +29687,7 @@
         <v>0.88</v>
       </c>
       <c r="AP134" t="n">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="AQ134" t="n">
         <v>1</v>
@@ -30126,7 +30126,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ136" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR136" t="n">
         <v>1.45</v>
@@ -31216,7 +31216,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ141" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="AR141" t="n">
         <v>1.16</v>
@@ -31649,7 +31649,7 @@
         <v>1.38</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ143" t="n">
         <v>1.25</v>
@@ -33175,7 +33175,7 @@
         <v>1.67</v>
       </c>
       <c r="AP150" t="n">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="AQ150" t="n">
         <v>1.5</v>
@@ -33396,7 +33396,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR151" t="n">
         <v>1.63</v>
@@ -33832,7 +33832,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="AR153" t="n">
         <v>2.06</v>
@@ -34047,7 +34047,7 @@
         <v>1.11</v>
       </c>
       <c r="AP154" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ154" t="n">
         <v>1</v>
@@ -36009,7 +36009,7 @@
         <v>0.4</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ163" t="n">
         <v>0.67</v>
@@ -36230,7 +36230,7 @@
         <v>1</v>
       </c>
       <c r="AQ164" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR164" t="n">
         <v>1.84</v>
@@ -36881,7 +36881,7 @@
         <v>1</v>
       </c>
       <c r="AP167" t="n">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="AQ167" t="n">
         <v>1.09</v>
@@ -37320,7 +37320,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="AR169" t="n">
         <v>2</v>
@@ -39279,7 +39279,7 @@
         <v>1.64</v>
       </c>
       <c r="AP178" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ178" t="n">
         <v>1.5</v>
@@ -39936,7 +39936,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ181" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="AR181" t="n">
         <v>2.41</v>
@@ -40151,7 +40151,7 @@
         <v>0.36</v>
       </c>
       <c r="AP182" t="n">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="AQ182" t="n">
         <v>0.38</v>
@@ -40590,7 +40590,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ184" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR184" t="n">
         <v>1.31</v>
@@ -42676,10 +42676,10 @@
         <v>0</v>
       </c>
       <c r="M194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O194" t="inlineStr">
         <is>
@@ -42688,7 +42688,7 @@
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>['-1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q194" t="n">
@@ -42767,10 +42767,10 @@
         <v>1.33</v>
       </c>
       <c r="AP194" t="n">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="AQ194" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="AR194" t="n">
         <v>1.51</v>
@@ -43224,13 +43224,13 @@
         <v>7</v>
       </c>
       <c r="AW196" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX196" t="n">
         <v>8</v>
       </c>
       <c r="AY196" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ196" t="n">
         <v>15</v>
@@ -43282,6 +43282,224 @@
       </c>
       <c r="BP196" t="n">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" t="n">
+        <v>8283072</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Czech Republic First League</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="n">
+        <v>46088.58333333334</v>
+      </c>
+      <c r="F197" t="n">
+        <v>25</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Jablonec</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Sigma Olomouc</t>
+        </is>
+      </c>
+      <c r="I197" t="n">
+        <v>0</v>
+      </c>
+      <c r="J197" t="n">
+        <v>1</v>
+      </c>
+      <c r="K197" t="n">
+        <v>1</v>
+      </c>
+      <c r="L197" t="n">
+        <v>1</v>
+      </c>
+      <c r="M197" t="n">
+        <v>2</v>
+      </c>
+      <c r="N197" t="n">
+        <v>3</v>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>['47']</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>['37', '88']</t>
+        </is>
+      </c>
+      <c r="Q197" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="R197" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="S197" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="T197" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U197" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V197" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="W197" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X197" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y197" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z197" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA197" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AB197" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AC197" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD197" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="AE197" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF197" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AG197" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH197" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI197" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ197" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AK197" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AL197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM197" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN197" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO197" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP197" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AQ197" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AR197" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS197" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AT197" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AU197" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV197" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW197" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX197" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY197" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ197" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA197" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB197" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC197" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD197" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BE197" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF197" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BG197" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH197" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI197" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BJ197" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BK197" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL197" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BM197" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BN197" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BO197" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BP197" t="n">
+        <v>1.37</v>
       </c>
     </row>
   </sheetData>
